--- a/results/Int Task Remove ACC 0.1/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_3_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6885748410038568</v>
+        <v>0.6962839728277548</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6841091101631177</v>
+        <v>0.6940511074073852</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.676322962232023</v>
+        <v>0.690397956666406</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6651778891569744</v>
+        <v>0.6921509756376392</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6488739402764157</v>
+        <v>0.6946079699637182</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6464292805612548</v>
+        <v>0.6860092419328636</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6534097678084705</v>
+        <v>0.6588051071306085</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6534097678084705</v>
+        <v>0.6547807146854072</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6562888465032882</v>
+        <v>0.6547807146854072</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6552906455514174</v>
+        <v>0.654947081510719</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6573956522000735</v>
+        <v>0.6594774938477368</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.657728385850697</v>
+        <v>0.6677627422547668</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6554762664035283</v>
+        <v>0.6658433564582218</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6708506068026883</v>
+        <v>0.666323202907358</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6708506068026883</v>
+        <v>0.666323202907358</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.665738662687501</v>
+        <v>0.6678590123887629</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6644654901654041</v>
+        <v>0.6683388588378991</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6639856437162679</v>
+        <v>0.6841036949680804</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6587774294670846</v>
+        <v>0.687264664649005</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6587774294670846</v>
+        <v>0.687264664649005</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6650277679167744</v>
+        <v>0.7096002382685815</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.66471428829295</v>
+        <v>0.6776800702771978</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6606390531832321</v>
+        <v>0.6776800702771978</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6321178226102444</v>
+        <v>0.6901945860083394</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6256433552548452</v>
+        <v>0.6882436115740769</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.632258015992876</v>
+        <v>0.6882436115740769</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6355206710028339</v>
+        <v>0.6746415441729493</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6441687374773615</v>
+        <v>0.672421013363498</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6059804812303323</v>
+        <v>0.6500908549389588</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6077527542283648</v>
+        <v>0.6554446777658108</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5989669011245555</v>
+        <v>0.6565707374893952</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.605742513492861</v>
+        <v>0.652360724192083</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.599651622452602</v>
+        <v>0.6487722549473823</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.599651622452602</v>
+        <v>0.6487530009205831</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6003170897538492</v>
+        <v>0.6503519876774229</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5972593096228016</v>
+        <v>0.6313807543968375</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5571101510839416</v>
+        <v>0.6313807543968375</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5396693120897238</v>
+        <v>0.6313807543968375</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5391894656405875</v>
+        <v>0.6343807724474877</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.542606152864939</v>
+        <v>0.6489425327468877</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5066754312601159</v>
+        <v>0.6441756568932424</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5118959801202173</v>
+        <v>0.6503874872893338</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5014864710377319</v>
+        <v>0.5835209598132359</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5014864710377319</v>
+        <v>0.5844999067383077</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4978140662699535</v>
+        <v>0.5950056859547892</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4932204766575009</v>
+        <v>0.6175076263996775</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4975583487265267</v>
+        <v>0.6207263581609997</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4996441013483836</v>
+        <v>0.6287366349978039</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5028559136938249</v>
+        <v>0.6297417553655558</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5099064976323564</v>
+        <v>0.6313669155650756</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5123057298780378</v>
+        <v>0.6385191848326404</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5172004645033965</v>
+        <v>0.6371127383437927</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5312823783536603</v>
+        <v>0.6123063315663753</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5187347697639577</v>
+        <v>0.5937255940168111</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5240708427848543</v>
+        <v>0.5869361428167438</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5536164477523932</v>
+        <v>0.5893161210356259</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5577440297474714</v>
+        <v>0.5787402451278287</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5718205284026979</v>
+        <v>0.577044988236993</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5637949085132883</v>
+        <v>0.56113995872418</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5297450646514119</v>
+        <v>0.5551961804824337</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5417866533492981</v>
+        <v>0.5575954127281151</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5459196505394136</v>
+        <v>0.5611853861936594</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5459196505394136</v>
+        <v>0.5399827917135482</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5454028002575226</v>
+        <v>0.5399827917135482</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.55336223442981</v>
+        <v>0.5529524846719895</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.560918838260158</v>
+        <v>0.547135060981113</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5369581044410616</v>
+        <v>0.5456955216337042</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5406359244038773</v>
+        <v>0.5466744685587759</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5346906419412872</v>
+        <v>0.5459704932039302</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5487147937111535</v>
+        <v>0.5509037358828873</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5187979470393925</v>
+        <v>0.5498754505141427</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5130713782874746</v>
+        <v>0.5454975661706749</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5061679071474557</v>
+        <v>0.5458757272907779</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5024377402992798</v>
+        <v>0.5410772627994151</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5035445459960649</v>
+        <v>0.5624901473534739</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5035445459960649</v>
+        <v>0.5074603336963519</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5027512199231042</v>
+        <v>0.5077738133201763</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5027512199231042</v>
+        <v>0.5073132208978394</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.503730166848176</v>
+        <v>0.5074795877231512</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5006654673012473</v>
+        <v>0.5130012815961589</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4998528872014874</v>
+        <v>0.5130012815961589</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4993922947791503</v>
+        <v>0.5025340104332757</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4993922947791503</v>
+        <v>0.500467511838218</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4993922947791503</v>
+        <v>0.4978895781563066</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4993922947791503</v>
+        <v>0.4973134615731744</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4986182227329887</v>
+        <v>0.4971663487746617</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4996865203761756</v>
+        <v>0.5004290037846196</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.5003712417042221</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.499725028429774</v>
       </c>
     </row>
   </sheetData>
